--- a/artfynd/A 9715-2024 artfynd.xlsx
+++ b/artfynd/A 9715-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119927239</v>
+        <v>119927273</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
+        <v>97885</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Granlidens naturreservat, Granlidens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>683033</v>
+        <v>683035</v>
       </c>
       <c r="R2" t="n">
-        <v>6687210</v>
+        <v>6687160</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119927891</v>
+        <v>119927884</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,37 +799,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brudgrind, Brudgrind, Upl</t>
@@ -917,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119927273</v>
+        <v>119927239</v>
       </c>
       <c r="B4" t="n">
-        <v>97885</v>
+        <v>97907</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,38 +911,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Granlidens naturreservat, Granlidens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>683035</v>
+        <v>683033</v>
       </c>
       <c r="R4" t="n">
-        <v>6687160</v>
+        <v>6687210</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -992,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119927884</v>
+        <v>119927891</v>
       </c>
       <c r="B5" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,28 +1032,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Brudgrind, Brudgrind, Upl</t>

--- a/artfynd/A 9715-2024 artfynd.xlsx
+++ b/artfynd/A 9715-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119927273</v>
+        <v>119927891</v>
       </c>
       <c r="B2" t="n">
-        <v>97885</v>
+        <v>97907</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Granlidens naturreservat, Granlidens naturreservat, Upl</t>
+          <t>Brudgrind, Brudgrind, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>683035</v>
+        <v>683065</v>
       </c>
       <c r="R2" t="n">
-        <v>6687160</v>
+        <v>6687107</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -787,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119927884</v>
+        <v>119927273</v>
       </c>
       <c r="B3" t="n">
-        <v>90527</v>
+        <v>97885</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +812,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>219798</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brudgrind, Brudgrind, Upl</t>
+          <t>Granlidens naturreservat, Granlidens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>683065</v>
+        <v>683035</v>
       </c>
       <c r="R3" t="n">
-        <v>6687107</v>
+        <v>6687160</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -899,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119927239</v>
+        <v>119927884</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,47 +920,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Granlidens naturreservat, Granlidens naturreservat, Upl</t>
+          <t>Brudgrind, Brudgrind, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>683033</v>
+        <v>683065</v>
       </c>
       <c r="R4" t="n">
-        <v>6687210</v>
+        <v>6687107</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119927891</v>
+        <v>119927239</v>
       </c>
       <c r="B5" t="n">
         <v>97907</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1065,14 +1065,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Brudgrind, Brudgrind, Upl</t>
+          <t>Granlidens naturreservat, Granlidens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683065</v>
+        <v>683033</v>
       </c>
       <c r="R5" t="n">
-        <v>6687107</v>
+        <v>6687210</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 9715-2024 artfynd.xlsx
+++ b/artfynd/A 9715-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119927891</v>
+        <v>119927884</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,37 +687,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brudgrind, Brudgrind, Upl</t>
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119927273</v>
+        <v>119927239</v>
       </c>
       <c r="B3" t="n">
-        <v>97885</v>
+        <v>97907</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,38 +799,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Granlidens naturreservat, Granlidens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>683035</v>
+        <v>683033</v>
       </c>
       <c r="R3" t="n">
-        <v>6687160</v>
+        <v>6687210</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119927884</v>
+        <v>119929531</v>
       </c>
       <c r="B4" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,38 +920,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Brudgrind, Brudgrind, Upl</t>
+          <t>Granlidens naturreservat, Granlidens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>683065</v>
+        <v>683014</v>
       </c>
       <c r="R4" t="n">
-        <v>6687107</v>
+        <v>6687196</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1020,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119927239</v>
+        <v>119927273</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>97885</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,47 +1041,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Granlidens naturreservat, Granlidens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683033</v>
+        <v>683035</v>
       </c>
       <c r="R5" t="n">
-        <v>6687210</v>
+        <v>6687160</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,7 +1141,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119929531</v>
+        <v>119927891</v>
       </c>
       <c r="B6" t="n">
         <v>97907</v>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1186,14 +1186,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Granlidens naturreservat, Granlidens naturreservat, Upl</t>
+          <t>Brudgrind, Brudgrind, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>683014</v>
+        <v>683065</v>
       </c>
       <c r="R6" t="n">
-        <v>6687196</v>
+        <v>6687107</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 9715-2024 artfynd.xlsx
+++ b/artfynd/A 9715-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119927884</v>
       </c>
       <c r="B2" t="n">
-        <v>90527</v>
+        <v>90545</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119927239</v>
+        <v>119929531</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>683033</v>
+        <v>683014</v>
       </c>
       <c r="R3" t="n">
-        <v>6687210</v>
+        <v>6687196</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119929531</v>
+        <v>119927239</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>683014</v>
+        <v>683033</v>
       </c>
       <c r="R4" t="n">
-        <v>6687196</v>
+        <v>6687210</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -992,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119927273</v>
+        <v>119927891</v>
       </c>
       <c r="B5" t="n">
-        <v>97885</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,38 +1041,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Granlidens naturreservat, Granlidens naturreservat, Upl</t>
+          <t>Brudgrind, Brudgrind, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683035</v>
+        <v>683065</v>
       </c>
       <c r="R5" t="n">
-        <v>6687160</v>
+        <v>6687107</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1141,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119927891</v>
+        <v>119927273</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>97908</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,47 +1162,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Brudgrind, Brudgrind, Upl</t>
+          <t>Granlidens naturreservat, Granlidens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>683065</v>
+        <v>683035</v>
       </c>
       <c r="R6" t="n">
-        <v>6687107</v>
+        <v>6687160</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 9715-2024 artfynd.xlsx
+++ b/artfynd/A 9715-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119927884</v>
+        <v>119929531</v>
       </c>
       <c r="B2" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Brudgrind, Brudgrind, Upl</t>
+          <t>Granlidens naturreservat, Granlidens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>683065</v>
+        <v>683014</v>
       </c>
       <c r="R2" t="n">
-        <v>6687107</v>
+        <v>6687196</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -787,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119929531</v>
+        <v>119927273</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>97908</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,47 +808,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Granlidens naturreservat, Granlidens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>683014</v>
+        <v>683035</v>
       </c>
       <c r="R3" t="n">
-        <v>6687196</v>
+        <v>6687160</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119927239</v>
+        <v>119927884</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,47 +920,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Granlidens naturreservat, Granlidens naturreservat, Upl</t>
+          <t>Brudgrind, Brudgrind, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>683033</v>
+        <v>683065</v>
       </c>
       <c r="R4" t="n">
-        <v>6687210</v>
+        <v>6687107</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -992,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1150,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119927273</v>
+        <v>119927239</v>
       </c>
       <c r="B6" t="n">
-        <v>97908</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,38 +1153,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Granlidens naturreservat, Granlidens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>683035</v>
+        <v>683033</v>
       </c>
       <c r="R6" t="n">
-        <v>6687160</v>
+        <v>6687210</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 9715-2024 artfynd.xlsx
+++ b/artfynd/A 9715-2024 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119927273</v>
+        <v>119927891</v>
       </c>
       <c r="B3" t="n">
-        <v>97908</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,38 +808,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Granlidens naturreservat, Granlidens naturreservat, Upl</t>
+          <t>Brudgrind, Brudgrind, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>683035</v>
+        <v>683065</v>
       </c>
       <c r="R3" t="n">
-        <v>6687160</v>
+        <v>6687107</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -1020,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119927891</v>
+        <v>119927273</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>97908</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,47 +1041,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Brudgrind, Brudgrind, Upl</t>
+          <t>Granlidens naturreservat, Granlidens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683065</v>
+        <v>683035</v>
       </c>
       <c r="R5" t="n">
-        <v>6687107</v>
+        <v>6687160</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 9715-2024 artfynd.xlsx
+++ b/artfynd/A 9715-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119929531</v>
+        <v>119927273</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>97908</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Granlidens naturreservat, Granlidens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>683014</v>
+        <v>683035</v>
       </c>
       <c r="R2" t="n">
-        <v>6687196</v>
+        <v>6687160</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -1029,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119927273</v>
+        <v>119927239</v>
       </c>
       <c r="B5" t="n">
-        <v>97908</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,38 +1032,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Granlidens naturreservat, Granlidens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683035</v>
+        <v>683033</v>
       </c>
       <c r="R5" t="n">
-        <v>6687160</v>
+        <v>6687210</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,7 +1141,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119927239</v>
+        <v>119929531</v>
       </c>
       <c r="B6" t="n">
         <v>97930</v>
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>683033</v>
+        <v>683014</v>
       </c>
       <c r="R6" t="n">
-        <v>6687210</v>
+        <v>6687196</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 9715-2024 artfynd.xlsx
+++ b/artfynd/A 9715-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119927273</v>
+        <v>119927239</v>
       </c>
       <c r="B2" t="n">
-        <v>97908</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Granlidens naturreservat, Granlidens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>683035</v>
+        <v>683033</v>
       </c>
       <c r="R2" t="n">
-        <v>6687160</v>
+        <v>6687210</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -908,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119927884</v>
+        <v>119927273</v>
       </c>
       <c r="B4" t="n">
-        <v>90545</v>
+        <v>97908</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,34 +933,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Brudgrind, Brudgrind, Upl</t>
+          <t>Granlidens naturreservat, Granlidens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>683065</v>
+        <v>683035</v>
       </c>
       <c r="R4" t="n">
-        <v>6687107</v>
+        <v>6687160</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1020,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119927239</v>
+        <v>119927884</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,47 +1041,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Granlidens naturreservat, Granlidens naturreservat, Upl</t>
+          <t>Brudgrind, Brudgrind, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683033</v>
+        <v>683065</v>
       </c>
       <c r="R5" t="n">
-        <v>6687210</v>
+        <v>6687107</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 9715-2024 artfynd.xlsx
+++ b/artfynd/A 9715-2024 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119927891</v>
+        <v>119927884</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,37 +808,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brudgrind, Brudgrind, Upl</t>
@@ -917,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119927273</v>
+        <v>119929531</v>
       </c>
       <c r="B4" t="n">
-        <v>97908</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,38 +920,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Granlidens naturreservat, Granlidens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>683035</v>
+        <v>683014</v>
       </c>
       <c r="R4" t="n">
-        <v>6687160</v>
+        <v>6687196</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119927884</v>
+        <v>119927273</v>
       </c>
       <c r="B5" t="n">
-        <v>90545</v>
+        <v>97908</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Brudgrind, Brudgrind, Upl</t>
+          <t>Granlidens naturreservat, Granlidens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683065</v>
+        <v>683035</v>
       </c>
       <c r="R5" t="n">
-        <v>6687107</v>
+        <v>6687160</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1141,7 +1141,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119929531</v>
+        <v>119927891</v>
       </c>
       <c r="B6" t="n">
         <v>97930</v>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1186,14 +1186,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Granlidens naturreservat, Granlidens naturreservat, Upl</t>
+          <t>Brudgrind, Brudgrind, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>683014</v>
+        <v>683065</v>
       </c>
       <c r="R6" t="n">
-        <v>6687196</v>
+        <v>6687107</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 9715-2024 artfynd.xlsx
+++ b/artfynd/A 9715-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119927239</v>
+        <v>119927273</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>97908</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Granlidens naturreservat, Granlidens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>683033</v>
+        <v>683035</v>
       </c>
       <c r="R2" t="n">
-        <v>6687210</v>
+        <v>6687160</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119927884</v>
+        <v>119929531</v>
       </c>
       <c r="B3" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,38 +799,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brudgrind, Brudgrind, Upl</t>
+          <t>Granlidens naturreservat, Granlidens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>683065</v>
+        <v>683014</v>
       </c>
       <c r="R3" t="n">
-        <v>6687107</v>
+        <v>6687196</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119929531</v>
+        <v>119927884</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,47 +920,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Granlidens naturreservat, Granlidens naturreservat, Upl</t>
+          <t>Brudgrind, Brudgrind, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>683014</v>
+        <v>683065</v>
       </c>
       <c r="R4" t="n">
-        <v>6687196</v>
+        <v>6687107</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1029,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119927273</v>
+        <v>119927891</v>
       </c>
       <c r="B5" t="n">
-        <v>97908</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,38 +1032,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Granlidens naturreservat, Granlidens naturreservat, Upl</t>
+          <t>Brudgrind, Brudgrind, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683035</v>
+        <v>683065</v>
       </c>
       <c r="R5" t="n">
-        <v>6687160</v>
+        <v>6687107</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1141,7 +1141,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119927891</v>
+        <v>119927239</v>
       </c>
       <c r="B6" t="n">
         <v>97930</v>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1186,14 +1186,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Brudgrind, Brudgrind, Upl</t>
+          <t>Granlidens naturreservat, Granlidens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>683065</v>
+        <v>683033</v>
       </c>
       <c r="R6" t="n">
-        <v>6687107</v>
+        <v>6687210</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
